--- a/assets/excel/corporate_sales_data.xlsx
+++ b/assets/excel/corporate_sales_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corporate Sales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Corporate Sales" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,8 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -475,17 +476,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEAL-000001</t>
+          <t>DEAL-0000001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>tanaka.yuki</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>株式会社ベータ製作所</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,8 +499,8 @@
           <t>中堅</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>126000000</v>
+      <c r="F2" s="1" t="n">
+        <v>460540000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -511,41 +512,41 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I2" s="1" t="n">
-        <v>46146</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>46334</v>
+      <c r="I2" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>46187</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEAL-000002</t>
+          <t>DEAL-0000002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>株式会社ゼータコーポレーション</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>16000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>10090000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -557,78 +558,78 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I3" s="1" t="n">
-        <v>46130</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>46290</v>
+      <c r="I3" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>46216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEAL-000003</t>
+          <t>DEAL-0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>沖縄リゾートグループ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>215000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>38350000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>46084</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>46232</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>46340</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEAL-000004</t>
+          <t>DEAL-0000004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>関東テクノサービス</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -636,12 +637,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>175000000</v>
+      <c r="F5" s="1" t="n">
+        <v>154800000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -649,41 +650,41 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>46247</v>
+      <c r="I5" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>46201</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEAL-000005</t>
+          <t>DEAL-0000005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>matsumoto.ayumi</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>カイ・アセットマネジメント</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>184000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>18810000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -692,35 +693,35 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>46126</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>46172</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>46184</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEAL-000006</t>
+          <t>DEAL-0000006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>sasaki.ryota</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>エータ精密工業</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -728,8 +729,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>41000000</v>
+      <c r="F7" s="1" t="n">
+        <v>22710000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -741,32 +742,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>46079</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>46319</v>
+      <c r="I7" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>46278</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEAL-000007</t>
+          <t>DEAL-0000007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>シータ・テクノロジーズ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -774,12 +775,12 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>24000000</v>
+      <c r="F8" s="1" t="n">
+        <v>200060000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -787,45 +788,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>46149</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>46220</v>
+      <c r="I8" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>46319</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEAL-000008</t>
+          <t>DEAL-0000008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>yamada.sakura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>新日本テレコム</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>326000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>14950000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -833,137 +834,137 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>46112</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>46251</v>
+      <c r="I9" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>46181</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEAL-000009</t>
+          <t>DEAL-0000009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>エータ精密工業</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>312000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>52280000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>46202</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>46255</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEAL-000010</t>
+          <t>DEAL-0000010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>yamada.sakura</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>クサイ重工業</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>113000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>80010000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>46130</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>46169</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>46204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DEAL-000011</t>
+          <t>DEAL-0000011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>播磨鋼材</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>109000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>4700000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -971,27 +972,27 @@
           <t>関西</t>
         </is>
       </c>
-      <c r="I12" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>46328</v>
+      <c r="I12" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>46324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEAL-000012</t>
+          <t>DEAL-0000012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>オミクロン食品株式会社</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1004,12 +1005,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>74000000</v>
+      <c r="F13" s="1" t="n">
+        <v>97820000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1017,87 +1018,87 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I13" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>46304</v>
+      <c r="I13" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>46241</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DEAL-000013</t>
+          <t>DEAL-0000013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>sasaki.ryota</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>シグマ建設株式会社</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>205000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>1082380000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>46291</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>46328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DEAL-000014</t>
+          <t>DEAL-0000014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>kimura.haruka</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>東北マテリアル株式会社</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>79000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>318000000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,35 +1107,35 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>46177</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>46224</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DEAL-000015</t>
+          <t>DEAL-0000015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>三友化学工業</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1142,35 +1143,35 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>271000000</v>
+      <c r="F16" s="1" t="n">
+        <v>335460000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>46335</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>46253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DEAL-000016</t>
+          <t>DEAL-0000016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1180,7 +1181,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1188,58 +1189,58 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>58000000</v>
+      <c r="F17" s="1" t="n">
+        <v>19980000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>46277</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>46200</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DEAL-000017</t>
+          <t>DEAL-0000017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>河内精密</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>260000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>85380000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1247,32 +1248,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>46078</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>46290</v>
+      <c r="I18" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>46258</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DEAL-000018</t>
+          <t>DEAL-0000018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>mori.yui</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>中国地方開発株式会社</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1280,12 +1281,12 @@
           <t>中堅</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>277000000</v>
+      <c r="F19" s="1" t="n">
+        <v>24160000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1293,32 +1294,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I19" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>46243</v>
+      <c r="I19" s="2" t="n">
+        <v>46072</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>46190</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DEAL-000019</t>
+          <t>DEAL-0000019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1326,12 +1327,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>450000000</v>
+      <c r="F20" s="1" t="n">
+        <v>7190000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1339,27 +1340,27 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>46222</v>
+      <c r="I20" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>46201</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DEAL-000020</t>
+          <t>DEAL-0000020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>inoue.shota</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>株式会社アルファ商事</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1369,125 +1370,125 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>418000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>111730000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>46193</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>46188</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DEAL-000021</t>
+          <t>DEAL-0000021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>北陸電子工業</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>271000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>14970000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>46299</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>46202</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DEAL-000022</t>
+          <t>DEAL-0000022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>摂津半導体</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>225000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>6000000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>46144</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>46224</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>46165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEAL-000023</t>
+          <t>DEAL-0000023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1497,7 +1498,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>オメガ・パートナーズ</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1507,15 +1508,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>302000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>16810000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1523,32 +1524,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I24" s="1" t="n">
-        <v>46084</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>46217</v>
+      <c r="I24" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>46181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DEAL-000024</t>
+          <t>DEAL-0000024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>takahashi.ichiro</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>播磨鋼材</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1556,12 +1557,12 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>118000000</v>
+      <c r="F25" s="1" t="n">
+        <v>206520000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1569,124 +1570,124 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I25" s="1" t="n">
-        <v>46117</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>46179</v>
+      <c r="I25" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>46329</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEAL-000025</t>
+          <t>DEAL-0000025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>kimura.haruka</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>大和精密機器</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>110000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>475280000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>46086</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>46308</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>46215</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DEAL-000026</t>
+          <t>DEAL-0000026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>デルタ電機株式会社</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>98000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>40360000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>46075</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>46271</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>46327</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DEAL-000027</t>
+          <t>DEAL-0000027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>yamada.sakura</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>関西フードサイエンス</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1694,8 +1695,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>443000000</v>
+      <c r="F28" s="1" t="n">
+        <v>37120000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1707,22 +1708,22 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>46152</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>46264</v>
+      <c r="I28" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>46177</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DEAL-000028</t>
+          <t>DEAL-0000028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>yoshida.hiroshi</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1732,38 +1733,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>98000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>139840000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>46142</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>46269</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>46131</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>46162</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DEAL-000029</t>
+          <t>DEAL-0000029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1773,71 +1774,71 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>紀州化成株式会社</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>448000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>19140000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>46089</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>46186</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>46245</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEAL-000030</t>
+          <t>DEAL-0000030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>takahashi.ichiro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>沖縄リゾートグループ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>475000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>295550000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1845,27 +1846,27 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>46285</v>
+      <c r="I31" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>46194</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DEAL-000031</t>
+          <t>DEAL-0000031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>デルタ電機株式会社</t>
+          <t>新日本テレコム</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1875,11 +1876,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>85000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>34970000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1888,30 +1889,30 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I32" s="1" t="n">
-        <v>46110</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>46228</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>46185</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEAL-000032</t>
+          <t>DEAL-0000032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>tanaka.yuki</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>常磐エネルギー</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1924,8 +1925,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>339000000</v>
+      <c r="F33" s="1" t="n">
+        <v>153360000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1934,20 +1935,20 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>46135</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>46236</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>46174</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DEAL-000033</t>
+          <t>DEAL-0000033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1957,12 +1958,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>デルタ電機株式会社</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1970,12 +1971,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>32000000</v>
+      <c r="F34" s="1" t="n">
+        <v>10520000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1983,45 +1984,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I34" s="1" t="n">
-        <v>46153</v>
-      </c>
-      <c r="J34" s="1" t="n">
-        <v>46310</v>
+      <c r="I34" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>46209</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEAL-000034</t>
+          <t>DEAL-0000034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>関西フードサイエンス</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>30000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>3900000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2029,32 +2030,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I35" s="1" t="n">
-        <v>46136</v>
-      </c>
-      <c r="J35" s="1" t="n">
-        <v>46178</v>
+      <c r="I35" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>46224</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DEAL-000035</t>
+          <t>DEAL-0000035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>takahashi.ichiro</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>デルタ電機株式会社</t>
+          <t>関西フードサイエンス</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2062,45 +2063,45 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>483000000</v>
+      <c r="F36" s="1" t="n">
+        <v>72900000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I36" s="1" t="n">
-        <v>46085</v>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>46313</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>46184</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DEAL-000036</t>
+          <t>DEAL-0000036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>ラムダ・キャピタル</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2108,45 +2109,45 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>337000000</v>
+      <c r="F37" s="1" t="n">
+        <v>63440000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I37" s="1" t="n">
-        <v>46093</v>
-      </c>
-      <c r="J37" s="1" t="n">
-        <v>46241</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>46176</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DEAL-000037</t>
+          <t>DEAL-0000037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>デルタ電機株式会社</t>
+          <t>北海道フロンティア商事</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2154,8 +2155,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>123000000</v>
+      <c r="F38" s="1" t="n">
+        <v>113840000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2164,66 +2165,66 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I38" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="J38" s="1" t="n">
-        <v>46332</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>46123</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DEAL-000038</t>
+          <t>DEAL-0000038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>常磐エネルギー</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>5000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>37790000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I39" s="1" t="n">
-        <v>46087</v>
-      </c>
-      <c r="J39" s="1" t="n">
-        <v>46186</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>46216</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DEAL-000039</t>
+          <t>DEAL-0000039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2233,12 +2234,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>東洋エレクトロニクス</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2246,8 +2247,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>136000000</v>
+      <c r="F40" s="1" t="n">
+        <v>9370000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2259,32 +2260,32 @@
           <t>関西</t>
         </is>
       </c>
-      <c r="I40" s="1" t="n">
-        <v>46151</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>46223</v>
+      <c r="I40" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>46173</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DEAL-000040</t>
+          <t>DEAL-0000040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>四国マリンプロダクツ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2292,12 +2293,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>427000000</v>
+      <c r="F41" s="1" t="n">
+        <v>141690000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2305,32 +2306,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I41" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="J41" s="1" t="n">
-        <v>46328</v>
+      <c r="I41" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>46181</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DEAL-000041</t>
+          <t>DEAL-0000041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>イプシロン物流株式会社</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2338,58 +2339,58 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>481000000</v>
+      <c r="F42" s="1" t="n">
+        <v>2530000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I42" s="1" t="n">
-        <v>46145</v>
-      </c>
-      <c r="J42" s="1" t="n">
-        <v>46188</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>46306</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DEAL-000042</t>
+          <t>DEAL-0000042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>takahashi.ichiro</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>東洋エレクトロニクス</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>108000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>33110000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2397,45 +2398,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I43" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="J43" s="1" t="n">
-        <v>46323</v>
+      <c r="I43" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>46329</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DEAL-000043</t>
+          <t>DEAL-0000043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>新日本テレコム</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>464000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>92760000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2443,87 +2444,87 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I44" s="1" t="n">
-        <v>46078</v>
-      </c>
-      <c r="J44" s="1" t="n">
-        <v>46269</v>
+      <c r="I44" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>46241</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DEAL-000044</t>
+          <t>DEAL-0000044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>株式会社ロー不動産</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>395000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>53610000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I45" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="J45" s="1" t="n">
-        <v>46274</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>46179</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DEAL-000045</t>
+          <t>DEAL-0000045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>sato.taro</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>中国地方開発株式会社</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>39000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>87820000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2532,30 +2533,30 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I46" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="J46" s="1" t="n">
-        <v>46255</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>46215</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEAL-000046</t>
+          <t>DEAL-0000046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>takahashi.ichiro</t>
+          <t>hayashi.takeshi</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>株式会社ロー不動産</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2565,15 +2566,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>158000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>22350000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2581,78 +2582,78 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I47" s="1" t="n">
-        <v>46114</v>
-      </c>
-      <c r="J47" s="1" t="n">
-        <v>46214</v>
+      <c r="I47" s="2" t="n">
+        <v>46112</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>46233</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DEAL-000047</t>
+          <t>DEAL-0000047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>関西フードサイエンス</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>453000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>291100000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I48" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="J48" s="1" t="n">
-        <v>46221</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>46331</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DEAL-000048</t>
+          <t>DEAL-0000048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>takahashi.ichiro</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>ウプシロン証券</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2660,91 +2661,91 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>92000000</v>
+      <c r="F49" s="1" t="n">
+        <v>58810000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>46074</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>46224</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>46188</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DEAL-000049</t>
+          <t>DEAL-0000049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>カッパ・ソリューションズ</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>196000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>108100000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I50" s="1" t="n">
-        <v>46131</v>
-      </c>
-      <c r="J50" s="1" t="n">
-        <v>46212</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>46116</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>46213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DEAL-000050</t>
+          <t>DEAL-0000050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>kobayashi.daiki</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>沖縄リゾートグループ</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2752,8 +2753,8 @@
           <t>中堅</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>115000000</v>
+      <c r="F51" s="1" t="n">
+        <v>8870000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2765,32 +2766,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I51" s="1" t="n">
-        <v>46108</v>
-      </c>
-      <c r="J51" s="1" t="n">
-        <v>46245</v>
+      <c r="I51" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DEAL-000051</t>
+          <t>DEAL-0000051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>kobayashi.daiki</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>ガンマホールディングス</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2798,58 +2799,58 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>329000000</v>
+      <c r="F52" s="1" t="n">
+        <v>216410000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>46298</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>46274</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DEAL-000052</t>
+          <t>DEAL-0000052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>紀州化成株式会社</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>92000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>23230000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2857,32 +2858,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I53" s="1" t="n">
-        <v>46155</v>
-      </c>
-      <c r="J53" s="1" t="n">
-        <v>46188</v>
+      <c r="I53" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>46337</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DEAL-000053</t>
+          <t>DEAL-0000053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>watanabe.kenji</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>三友化学工業</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2890,8 +2891,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>224000000</v>
+      <c r="F54" s="1" t="n">
+        <v>54570000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2903,32 +2904,32 @@
           <t>九州</t>
         </is>
       </c>
-      <c r="I54" s="1" t="n">
-        <v>46145</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>46259</v>
+      <c r="I54" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>46271</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DEAL-000054</t>
+          <t>DEAL-0000054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>watanabe.kenji</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>ガンマホールディングス</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2936,132 +2937,132 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1000000</v>
+      <c r="F55" s="1" t="n">
+        <v>5130000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I55" s="1" t="n">
-        <v>46072</v>
-      </c>
-      <c r="J55" s="1" t="n">
-        <v>46332</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>46335</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DEAL-000055</t>
+          <t>DEAL-0000055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>常磐エネルギー</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>486000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>123000000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>46330</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>46200</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DEAL-000056</t>
+          <t>DEAL-0000056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>ラムダ・キャピタル</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>342000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>8420000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>46108</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>46339</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>46117</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>46266</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DEAL-000057</t>
+          <t>DEAL-0000057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>シグマ建設株式会社</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3071,11 +3072,11 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>216000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>21310000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3087,41 +3088,41 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I58" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>46306</v>
+      <c r="I58" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>46217</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DEAL-000058</t>
+          <t>DEAL-0000058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>yamamoto.akira</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>中国地方開発株式会社</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>156000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>133200000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3133,78 +3134,78 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I59" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>46309</v>
+      <c r="I59" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>46329</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DEAL-000059</t>
+          <t>DEAL-0000059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>yamamoto.akira</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>東北マテリアル株式会社</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>346000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>20550000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I60" s="1" t="n">
-        <v>46099</v>
-      </c>
-      <c r="J60" s="1" t="n">
-        <v>46204</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>46325</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DEAL-000060</t>
+          <t>DEAL-0000060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>hayashi.takeshi</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>東北マテリアル株式会社</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -3212,12 +3213,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>172000000</v>
+      <c r="F61" s="1" t="n">
+        <v>167920000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3225,32 +3226,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I61" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="J61" s="1" t="n">
-        <v>46240</v>
+      <c r="I61" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>46227</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DEAL-000061</t>
+          <t>DEAL-0000061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>デルタ電機株式会社</t>
+          <t>東洋エレクトロニクス</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3258,45 +3259,45 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>24000000</v>
+      <c r="F62" s="1" t="n">
+        <v>251160000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I62" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="J62" s="1" t="n">
-        <v>46179</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>46249</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DEAL-000062</t>
+          <t>DEAL-0000062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>yoshida.hiroshi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>エータ精密工業</t>
+          <t>中部オートメーション</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3304,45 +3305,45 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>100000000</v>
+      <c r="F63" s="1" t="n">
+        <v>924720000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I63" s="1" t="n">
-        <v>46108</v>
-      </c>
-      <c r="J63" s="1" t="n">
-        <v>46223</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>46209</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DEAL-000063</t>
+          <t>DEAL-0000063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>takahashi.ichiro</t>
+          <t>kobayashi.daiki</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>ガンマホールディングス</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3350,8 +3351,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>113000000</v>
+      <c r="F64" s="1" t="n">
+        <v>132480000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3363,27 +3364,27 @@
           <t>九州</t>
         </is>
       </c>
-      <c r="I64" s="1" t="n">
-        <v>46100</v>
-      </c>
-      <c r="J64" s="1" t="n">
-        <v>46173</v>
+      <c r="I64" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>46336</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DEAL-000064</t>
+          <t>DEAL-0000064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>yamamoto.akira</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>オメガ・パートナーズ</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3393,48 +3394,48 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>411000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>22100000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>九州</t>
-        </is>
-      </c>
-      <c r="I65" s="1" t="n">
-        <v>46088</v>
-      </c>
-      <c r="J65" s="1" t="n">
-        <v>46313</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>46330</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DEAL-000065</t>
+          <t>DEAL-0000065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>tanaka.yuki</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>播磨鋼材</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3442,40 +3443,40 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>219000000</v>
+      <c r="F66" s="1" t="n">
+        <v>50820000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I66" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="J66" s="1" t="n">
-        <v>46282</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>46264</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DEAL-000066</t>
+          <t>DEAL-0000066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>大和精密機器</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3488,8 +3489,8 @@
           <t>中堅</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>393000000</v>
+      <c r="F67" s="1" t="n">
+        <v>319310000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3498,112 +3499,112 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I67" s="1" t="n">
-        <v>46079</v>
-      </c>
-      <c r="J67" s="1" t="n">
-        <v>46222</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>46205</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DEAL-000067</t>
+          <t>DEAL-0000067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>mori.yui</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>新日本テレコム</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>121000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>35770000</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I68" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="J68" s="1" t="n">
-        <v>46299</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>46234</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DEAL-000068</t>
+          <t>DEAL-0000068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>yamamoto.akira</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>中部オートメーション</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>197000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>189810000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I69" s="1" t="n">
-        <v>46151</v>
-      </c>
-      <c r="J69" s="1" t="n">
-        <v>46267</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>46274</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DEAL-000069</t>
+          <t>DEAL-0000069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3613,21 +3614,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>沖縄リゾートグループ</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>213000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>78890000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3639,41 +3640,41 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I70" s="1" t="n">
-        <v>46106</v>
-      </c>
-      <c r="J70" s="1" t="n">
-        <v>46260</v>
+      <c r="I70" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>46330</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DEAL-000070</t>
+          <t>DEAL-0000070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>mori.yui</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>カイ・アセットマネジメント</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>4000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>5360000</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3685,27 +3686,27 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I71" s="1" t="n">
-        <v>46110</v>
-      </c>
-      <c r="J71" s="1" t="n">
-        <v>46268</v>
+      <c r="I71" s="2" t="n">
+        <v>46134</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>46198</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DEAL-000071</t>
+          <t>DEAL-0000071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>sato.taro</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>ガンマホールディングス</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3715,15 +3716,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>224000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>939710000</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3731,63 +3732,63 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I72" s="1" t="n">
-        <v>46110</v>
-      </c>
-      <c r="J72" s="1" t="n">
-        <v>46247</v>
+      <c r="I72" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>46267</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>DEAL-000072</t>
+          <t>DEAL-0000072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>ニュー・エネルギー株式会社</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>公共</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>319000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>50560000</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="n">
-        <v>46109</v>
-      </c>
-      <c r="J73" s="1" t="n">
-        <v>46312</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>46198</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DEAL-000073</t>
+          <t>DEAL-0000073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3797,12 +3798,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3810,12 +3811,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>70000000</v>
+      <c r="F74" s="1" t="n">
+        <v>107010000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3823,179 +3824,179 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I74" s="1" t="n">
-        <v>46153</v>
-      </c>
-      <c r="J74" s="1" t="n">
-        <v>46227</v>
+      <c r="I74" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>46293</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DEAL-000074</t>
+          <t>DEAL-0000074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>inoue.shota</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>デルタ電機株式会社</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>168000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>117270000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I75" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="J75" s="1" t="n">
-        <v>46268</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>DEAL-000075</t>
+          <t>DEAL-0000075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>hayashi.takeshi</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>大和精密機器</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>384000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>51440000</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I76" s="1" t="n">
-        <v>46115</v>
-      </c>
-      <c r="J76" s="1" t="n">
-        <v>46218</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>46270</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DEAL-000076</t>
+          <t>DEAL-0000076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>shimizu.nana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>株式会社アルファ商事</t>
+          <t>関西フードサイエンス</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>103000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>38600000</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="J77" s="1" t="n">
-        <v>46222</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>46128</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>46324</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DEAL-000077</t>
+          <t>DEAL-0000077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>takahashi.ichiro</t>
+          <t>kobayashi.daiki</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>摂津半導体</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>289000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>113240000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4004,35 +4005,35 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>中部</t>
-        </is>
-      </c>
-      <c r="I78" s="1" t="n">
-        <v>46070</v>
-      </c>
-      <c r="J78" s="1" t="n">
-        <v>46226</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>46180</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DEAL-000078</t>
+          <t>DEAL-0000078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>株式会社パイ通信</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4040,54 +4041,54 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>494000000</v>
+      <c r="F79" s="1" t="n">
+        <v>18520000</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I79" s="1" t="n">
-        <v>46120</v>
-      </c>
-      <c r="J79" s="1" t="n">
-        <v>46188</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>46196</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DEAL-000079</t>
+          <t>DEAL-0000079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>watanabe.kenji</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>オミクロン食品株式会社</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>204000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>264870000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4099,45 +4100,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I80" s="1" t="n">
-        <v>46084</v>
-      </c>
-      <c r="J80" s="1" t="n">
-        <v>46337</v>
+      <c r="I80" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>46265</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DEAL-000080</t>
+          <t>DEAL-0000080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>yoshida.hiroshi</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>三友化学工業</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>436000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>6460000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4145,32 +4146,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I81" s="1" t="n">
-        <v>46087</v>
-      </c>
-      <c r="J81" s="1" t="n">
-        <v>46171</v>
+      <c r="I81" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>46260</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DEAL-000081</t>
+          <t>DEAL-0000081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>阪神物流システム</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4178,8 +4179,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>36000000</v>
+      <c r="F82" s="1" t="n">
+        <v>89200000</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4188,30 +4189,30 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I82" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="J82" s="1" t="n">
-        <v>46268</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>46251</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DEAL-000082</t>
+          <t>DEAL-0000082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4224,45 +4225,45 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>326000000</v>
+      <c r="F83" s="1" t="n">
+        <v>304410000</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I83" s="1" t="n">
-        <v>46104</v>
-      </c>
-      <c r="J83" s="1" t="n">
-        <v>46206</v>
+          <t>九州</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>46217</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DEAL-000083</t>
+          <t>DEAL-0000083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>kimura.haruka</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>オミクロン食品株式会社</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>サービス</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -4270,8 +4271,8 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>239000000</v>
+      <c r="F84" s="1" t="n">
+        <v>115090000</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4280,35 +4281,35 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I84" s="1" t="n">
-        <v>46125</v>
-      </c>
-      <c r="J84" s="1" t="n">
-        <v>46243</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>46247</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DEAL-000084</t>
+          <t>DEAL-0000084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>sasaki.ryota</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>播磨鋼材</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -4316,12 +4317,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>125000000</v>
+      <c r="F85" s="1" t="n">
+        <v>8290000</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4329,63 +4330,63 @@
           <t>海外</t>
         </is>
       </c>
-      <c r="I85" s="1" t="n">
-        <v>46081</v>
-      </c>
-      <c r="J85" s="1" t="n">
-        <v>46332</v>
+      <c r="I85" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>46167</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DEAL-000085</t>
+          <t>DEAL-0000085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>yamamoto.akira</t>
+          <t>sasaki.ryota</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>東洋エレクトロニクス</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>436000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>365220000</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I86" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="J86" s="1" t="n">
-        <v>46215</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>46279</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DEAL-000086</t>
+          <t>DEAL-0000086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4395,7 +4396,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>イプシロン物流株式会社</t>
+          <t>デルタ電機株式会社</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -4405,15 +4406,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>451000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>135570000</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4421,45 +4422,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I87" s="1" t="n">
-        <v>46088</v>
-      </c>
-      <c r="J87" s="1" t="n">
-        <v>46163</v>
+      <c r="I87" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>46244</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DEAL-000087</t>
+          <t>DEAL-0000087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>yoshida.hiroshi</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>251000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>5160000</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4467,32 +4468,32 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I88" s="1" t="n">
-        <v>46071</v>
-      </c>
-      <c r="J88" s="1" t="n">
-        <v>46282</v>
+      <c r="I88" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>46281</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DEAL-000088</t>
+          <t>DEAL-0000088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>nakamura.rie</t>
+          <t>sato.taro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>但馬農産加工</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4500,8 +4501,8 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>151000000</v>
+      <c r="F89" s="1" t="n">
+        <v>14810000</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4510,94 +4511,94 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I89" s="1" t="n">
-        <v>46071</v>
-      </c>
-      <c r="J89" s="1" t="n">
-        <v>46223</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>46178</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>DEAL-000089</t>
+          <t>DEAL-0000089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>suzuki.hanako</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>丹波食品工業</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>製造</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>284000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>17410000</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>関西</t>
-        </is>
-      </c>
-      <c r="I90" s="1" t="n">
-        <v>46105</v>
-      </c>
-      <c r="J90" s="1" t="n">
-        <v>46301</v>
+          <t>関東</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>46200</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DEAL-000090</t>
+          <t>DEAL-0000090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>nakamura.rie</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>株式会社イオタファイナンス</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>公共</t>
+          <t>小売</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>139000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>13140000</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4605,73 +4606,73 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I91" s="1" t="n">
-        <v>46130</v>
-      </c>
-      <c r="J91" s="1" t="n">
-        <v>46191</v>
+      <c r="I91" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>46340</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DEAL-000091</t>
+          <t>DEAL-0000091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>kobayashi.daiki</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>株式会社ゼータコーポレーション</t>
+          <t>摂津半導体</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>製造</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>487000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>8710000</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I92" s="1" t="n">
-        <v>46132</v>
-      </c>
-      <c r="J92" s="1" t="n">
-        <v>46284</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>46202</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DEAL-000092</t>
+          <t>DEAL-0000092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>エータ精密工業</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4681,48 +4682,48 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>145000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>18010000</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I93" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="J93" s="1" t="n">
-        <v>46219</v>
+          <t>海外</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>46073</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>46257</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DEAL-000093</t>
+          <t>DEAL-0000093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ito.mai</t>
+          <t>sasaki.ryota</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ガンマホールディングス</t>
+          <t>紀州化成株式会社</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4730,8 +4731,8 @@
           <t>大手</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>363000000</v>
+      <c r="F94" s="1" t="n">
+        <v>17570000</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4743,45 +4744,45 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I94" s="1" t="n">
-        <v>46124</v>
-      </c>
-      <c r="J94" s="1" t="n">
-        <v>46172</v>
+      <c r="I94" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>46339</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DEAL-000094</t>
+          <t>DEAL-0000094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>sato.taro</t>
+          <t>kato.megumi</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>京浜重機工業</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>サービス</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>327000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>9490000</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4789,73 +4790,73 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I95" s="1" t="n">
-        <v>46158</v>
-      </c>
-      <c r="J95" s="1" t="n">
-        <v>46307</v>
+      <c r="I95" s="2" t="n">
+        <v>46115</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>46297</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>DEAL-000095</t>
+          <t>DEAL-0000095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>matsumoto.ayumi</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>シータ・テクノロジーズ</t>
+          <t>常磐エネルギー</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>175000000</v>
+          <t>大手</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>194230000</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I96" s="1" t="n">
-        <v>46127</v>
-      </c>
-      <c r="J96" s="1" t="n">
-        <v>46283</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>46268</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>DEAL-000096</t>
+          <t>DEAL-0000096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>suzuki.hanako</t>
+          <t>kimura.haruka</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>エータ精密工業</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4868,12 +4869,12 @@
           <t>中小</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>38000000</v>
+      <c r="F97" s="1" t="n">
+        <v>86080000</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>受注</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4881,91 +4882,91 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I97" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="J97" s="1" t="n">
-        <v>46199</v>
+      <c r="I97" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>46206</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>DEAL-000097</t>
+          <t>DEAL-0000097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>hayashi.takeshi</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>信越バイオテック</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>286000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>490760000</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>失注</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>海外</t>
-        </is>
-      </c>
-      <c r="I98" s="1" t="n">
-        <v>46083</v>
-      </c>
-      <c r="J98" s="1" t="n">
-        <v>46319</v>
+          <t>中部</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>46272</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>DEAL-000098</t>
+          <t>DEAL-0000098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>tanaka.yuki</t>
+          <t>saito.kentaro</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>株式会社イオタファイナンス</t>
+          <t>シグマ建設株式会社</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>小売</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>中小</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>466000000</v>
+          <t>中堅</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>53260000</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>受注</t>
+          <t>提案</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4973,27 +4974,27 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I99" s="1" t="n">
-        <v>46084</v>
-      </c>
-      <c r="J99" s="1" t="n">
-        <v>46270</v>
+      <c r="I99" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>46223</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DEAL-000099</t>
+          <t>DEAL-0000099</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>inoue.shota</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>カッパ・ソリューションズ</t>
+          <t>新日本テレコム</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5003,15 +5004,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>大手</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>313000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>33630000</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>提案</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5019,27 +5020,27 @@
           <t>関東</t>
         </is>
       </c>
-      <c r="I100" s="1" t="n">
-        <v>46079</v>
-      </c>
-      <c r="J100" s="1" t="n">
-        <v>46215</v>
+      <c r="I100" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>46244</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>DEAL-000100</t>
+          <t>DEAL-0000100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>watanabe.kenji</t>
+          <t>ito.mai</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>株式会社ベータ製作所</t>
+          <t>九州エナジー株式会社</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5049,27 +5050,27 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>中堅</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>89000000</v>
+          <t>中小</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>6810000</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>失注</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>関東</t>
-        </is>
-      </c>
-      <c r="I101" s="1" t="n">
-        <v>46139</v>
-      </c>
-      <c r="J101" s="1" t="n">
-        <v>46161</v>
+          <t>関西</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>46124</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>46313</v>
       </c>
     </row>
   </sheetData>
